--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1081" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4852C4D4-A405-5D44-8996-343B4449A7F9}"/>
+  <xr:revisionPtr revIDLastSave="1248" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B06864A1-7FDC-7246-AC94-E96E57DDAEEC}"/>
   <bookViews>
     <workbookView xWindow="5300" yWindow="820" windowWidth="40220" windowHeight="25920" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -76,12 +76,15 @@
   <si>
     <t>Aarau</t>
   </si>
+  <si>
+    <t>St. Gallen</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -99,6 +102,12 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -135,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -145,6 +154,7 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -479,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:F398"/>
+  <dimension ref="A1:G459"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -4895,7 +4905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>45961</v>
       </c>
@@ -4903,7 +4913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>45975</v>
       </c>
@@ -4911,7 +4921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>45959</v>
       </c>
@@ -4919,7 +4929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>45981</v>
       </c>
@@ -4927,7 +4937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>45960</v>
       </c>
@@ -4935,7 +4945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>45979</v>
       </c>
@@ -4943,7 +4953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>45967</v>
       </c>
@@ -4951,7 +4961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>45958</v>
       </c>
@@ -4959,7 +4969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>45961</v>
       </c>
@@ -4967,20 +4977,794 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A394" s="1"/>
-    </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A395" s="1"/>
-    </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A396" s="1"/>
-    </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A397" s="1"/>
-    </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A398" s="1"/>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A394" s="7">
+        <v>46001</v>
+      </c>
+      <c r="B394" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+      <c r="D394" s="8">
+        <v>1</v>
+      </c>
+      <c r="E394" s="8"/>
+      <c r="F394" s="8"/>
+      <c r="G394" s="8"/>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A395" s="7">
+        <v>46001</v>
+      </c>
+      <c r="B395" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+      <c r="D395" s="8">
+        <v>0</v>
+      </c>
+      <c r="E395" s="8"/>
+      <c r="F395" s="8"/>
+      <c r="G395" s="8"/>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A396" s="7">
+        <v>46000</v>
+      </c>
+      <c r="B396" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+      <c r="D396" s="8">
+        <v>1</v>
+      </c>
+      <c r="E396" s="8"/>
+      <c r="F396" s="8"/>
+      <c r="G396" s="8"/>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A397" s="7">
+        <v>46000</v>
+      </c>
+      <c r="B397" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C397">
+        <v>1</v>
+      </c>
+      <c r="D397" s="8">
+        <v>1</v>
+      </c>
+      <c r="E397" s="8"/>
+      <c r="F397" s="8"/>
+      <c r="G397" s="8"/>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A398" s="7">
+        <v>45999</v>
+      </c>
+      <c r="B398" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+      <c r="D398" s="8">
+        <v>1</v>
+      </c>
+      <c r="E398" s="8"/>
+      <c r="F398" s="8"/>
+      <c r="G398" s="8"/>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A399" s="7">
+        <v>45999</v>
+      </c>
+      <c r="B399" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+      <c r="D399" s="8">
+        <v>0</v>
+      </c>
+      <c r="E399" s="8"/>
+      <c r="F399" s="8"/>
+      <c r="G399" s="8"/>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A400" s="7">
+        <v>45999</v>
+      </c>
+      <c r="B400" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+      <c r="D400" s="8">
+        <v>0</v>
+      </c>
+      <c r="E400" s="8"/>
+      <c r="F400" s="8"/>
+      <c r="G400" s="8"/>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A401" s="7">
+        <v>45999</v>
+      </c>
+      <c r="B401" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+      <c r="D401" s="8">
+        <v>1</v>
+      </c>
+      <c r="E401" s="8"/>
+      <c r="F401" s="8"/>
+      <c r="G401" s="8"/>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A402" s="7">
+        <v>45996</v>
+      </c>
+      <c r="B402" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+      <c r="D402" s="8">
+        <v>0</v>
+      </c>
+      <c r="E402" s="8"/>
+      <c r="F402" s="8"/>
+      <c r="G402" s="8"/>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A403" s="7">
+        <v>45995</v>
+      </c>
+      <c r="B403" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+      <c r="D403" s="8">
+        <v>1</v>
+      </c>
+      <c r="E403" s="8"/>
+      <c r="F403" s="8"/>
+      <c r="G403" s="8"/>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A404" s="7">
+        <v>45995</v>
+      </c>
+      <c r="B404" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+      <c r="D404" s="8">
+        <v>0</v>
+      </c>
+      <c r="E404" s="9"/>
+      <c r="F404" s="8"/>
+      <c r="G404" s="8"/>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A405" s="7">
+        <v>45994</v>
+      </c>
+      <c r="B405" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+      <c r="D405" s="8">
+        <v>0</v>
+      </c>
+      <c r="E405" s="9"/>
+      <c r="F405" s="8"/>
+      <c r="G405" s="8"/>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A406" s="7">
+        <v>45994</v>
+      </c>
+      <c r="B406" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+      <c r="D406" s="8">
+        <v>0</v>
+      </c>
+      <c r="E406" s="9"/>
+      <c r="F406" s="8"/>
+      <c r="G406" s="8"/>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A407" s="7">
+        <v>45993</v>
+      </c>
+      <c r="B407" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+      <c r="D407" s="8">
+        <v>0</v>
+      </c>
+      <c r="E407" s="9"/>
+      <c r="F407" s="8"/>
+      <c r="G407" s="8"/>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A408" s="7">
+        <v>45993</v>
+      </c>
+      <c r="B408" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+      <c r="D408" s="8">
+        <v>1</v>
+      </c>
+      <c r="E408" s="9"/>
+      <c r="F408" s="8"/>
+      <c r="G408" s="8"/>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A409" s="7">
+        <v>45992</v>
+      </c>
+      <c r="B409" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C409">
+        <v>1</v>
+      </c>
+      <c r="D409" s="8">
+        <v>0</v>
+      </c>
+      <c r="E409" s="9"/>
+      <c r="F409" s="8"/>
+      <c r="G409" s="8"/>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A410" s="7">
+        <v>45989</v>
+      </c>
+      <c r="B410" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+      <c r="D410" s="8">
+        <v>0</v>
+      </c>
+      <c r="E410" s="9"/>
+      <c r="F410" s="8"/>
+      <c r="G410" s="8"/>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A411" s="7">
+        <v>45989</v>
+      </c>
+      <c r="B411" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+      <c r="D411" s="8">
+        <v>0</v>
+      </c>
+      <c r="E411" s="9"/>
+      <c r="F411" s="8"/>
+      <c r="G411" s="8"/>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A412" s="7">
+        <v>45988</v>
+      </c>
+      <c r="B412" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C412">
+        <v>1</v>
+      </c>
+      <c r="D412" s="8">
+        <v>0</v>
+      </c>
+      <c r="E412" s="8"/>
+      <c r="F412" s="8"/>
+      <c r="G412" s="8"/>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A413" s="7">
+        <v>45988</v>
+      </c>
+      <c r="B413" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+      <c r="D413" s="8">
+        <v>0</v>
+      </c>
+      <c r="E413" s="8"/>
+      <c r="F413" s="8"/>
+      <c r="G413" s="8"/>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A414" s="7">
+        <v>45988</v>
+      </c>
+      <c r="B414" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C414">
+        <v>1</v>
+      </c>
+      <c r="D414" s="8">
+        <v>0</v>
+      </c>
+      <c r="E414" s="8"/>
+      <c r="F414" s="8"/>
+      <c r="G414" s="8"/>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A415" s="7">
+        <v>45987</v>
+      </c>
+      <c r="B415" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C415">
+        <v>1</v>
+      </c>
+      <c r="D415" s="8">
+        <v>0</v>
+      </c>
+      <c r="E415" s="8"/>
+      <c r="F415" s="8"/>
+      <c r="G415" s="8"/>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A416" s="7">
+        <v>45987</v>
+      </c>
+      <c r="B416" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C416">
+        <v>1</v>
+      </c>
+      <c r="D416" s="8">
+        <v>0</v>
+      </c>
+      <c r="E416" s="8"/>
+      <c r="F416" s="8"/>
+      <c r="G416" s="8"/>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A417" s="7">
+        <v>45986</v>
+      </c>
+      <c r="B417" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+      <c r="D417" s="8">
+        <v>0</v>
+      </c>
+      <c r="E417" s="8"/>
+      <c r="F417" s="8"/>
+      <c r="G417" s="8"/>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A418" s="7">
+        <v>45986</v>
+      </c>
+      <c r="B418" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C418">
+        <v>1</v>
+      </c>
+      <c r="D418" s="8">
+        <v>1</v>
+      </c>
+      <c r="E418" s="8"/>
+      <c r="F418" s="8"/>
+      <c r="G418" s="8"/>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A419" s="7">
+        <v>45986</v>
+      </c>
+      <c r="B419" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C419">
+        <v>1</v>
+      </c>
+      <c r="D419" s="8">
+        <v>0</v>
+      </c>
+      <c r="E419" s="8"/>
+      <c r="F419" s="8"/>
+      <c r="G419" s="8"/>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A420" s="7">
+        <v>45985</v>
+      </c>
+      <c r="B420" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C420">
+        <v>1</v>
+      </c>
+      <c r="D420" s="8">
+        <v>0</v>
+      </c>
+      <c r="E420" s="8"/>
+      <c r="F420" s="8"/>
+      <c r="G420" s="8"/>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A421" s="7">
+        <v>45985</v>
+      </c>
+      <c r="B421" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C421">
+        <v>1</v>
+      </c>
+      <c r="D421" s="8">
+        <v>1</v>
+      </c>
+      <c r="E421" s="8"/>
+      <c r="F421" s="8"/>
+      <c r="G421" s="8"/>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A422" s="7">
+        <v>45982</v>
+      </c>
+      <c r="B422" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C422">
+        <v>1</v>
+      </c>
+      <c r="D422" s="8">
+        <v>1</v>
+      </c>
+      <c r="E422" s="8"/>
+      <c r="F422" s="8"/>
+      <c r="G422" s="8"/>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A423" s="4">
+        <v>45982</v>
+      </c>
+      <c r="E423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A424" s="4">
+        <v>45985</v>
+      </c>
+      <c r="E424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A425" s="4">
+        <v>45986</v>
+      </c>
+      <c r="E425">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A426" s="4">
+        <v>45987</v>
+      </c>
+      <c r="E426">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A427" s="4">
+        <v>45989</v>
+      </c>
+      <c r="E427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A428" s="4">
+        <v>45992</v>
+      </c>
+      <c r="E428">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A429" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E429">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A430" s="4">
+        <v>45994</v>
+      </c>
+      <c r="E430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A431" s="4">
+        <v>45995</v>
+      </c>
+      <c r="E431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A432" s="4">
+        <v>45996</v>
+      </c>
+      <c r="E432">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A433" s="4">
+        <v>45999</v>
+      </c>
+      <c r="E433">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A434" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A435" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E435">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A436" s="4">
+        <v>45985</v>
+      </c>
+      <c r="E436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A437" s="4">
+        <v>45987</v>
+      </c>
+      <c r="E437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A438" s="4">
+        <v>45988</v>
+      </c>
+      <c r="E438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A439" s="4">
+        <v>45994</v>
+      </c>
+      <c r="E439">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A440" s="4">
+        <v>45994</v>
+      </c>
+      <c r="E440">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A441" s="4">
+        <v>45996</v>
+      </c>
+      <c r="E441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A442" s="4">
+        <v>45982</v>
+      </c>
+      <c r="E442">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A443" s="4">
+        <v>45986</v>
+      </c>
+      <c r="E443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A444" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A445" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A446" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A447" s="4">
+        <v>45989</v>
+      </c>
+      <c r="E447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A448" s="4">
+        <v>45992</v>
+      </c>
+      <c r="E448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A449" s="4">
+        <v>45995</v>
+      </c>
+      <c r="E449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A450" s="4">
+        <v>45987</v>
+      </c>
+      <c r="E450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A451" s="4">
+        <v>45988</v>
+      </c>
+      <c r="E451">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A452" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A453" s="4">
+        <v>45994</v>
+      </c>
+      <c r="E453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A454" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E454">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A455" s="4">
+        <v>45982</v>
+      </c>
+      <c r="E455">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A456" s="4">
+        <v>45985</v>
+      </c>
+      <c r="E456">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A457" s="4">
+        <v>45999</v>
+      </c>
+      <c r="E457">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A458" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E458">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A459" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E459">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A209:A237">
@@ -4991,16 +5775,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
-    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
-    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5221,39 +6001,58 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
+    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
+    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46834C1C-4F65-47EA-B4E5-1EFA1FE1385B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46834C1C-4F65-47EA-B4E5-1EFA1FE1385B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1248" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B06864A1-7FDC-7246-AC94-E96E57DDAEEC}"/>
+  <xr:revisionPtr revIDLastSave="1354" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF22474B-1145-8840-B1CA-F149940F1752}"/>
   <bookViews>
     <workbookView xWindow="5300" yWindow="820" windowWidth="40220" windowHeight="25920" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -489,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:G459"/>
+  <dimension ref="A1:G492"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -5678,7 +5678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A449" s="4">
         <v>45995</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A450" s="4">
         <v>45987</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A451" s="4">
         <v>45988</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" s="4">
         <v>45993</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
         <v>45994</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" s="4">
         <v>46000</v>
       </c>
@@ -5726,7 +5726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A455" s="4">
         <v>45982</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A456" s="4">
         <v>45985</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A457" s="4">
         <v>45999</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A458" s="4">
         <v>46000</v>
       </c>
@@ -5758,11 +5758,403 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A459" s="4">
         <v>46001</v>
       </c>
       <c r="E459">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A460" s="7">
+        <v>46010</v>
+      </c>
+      <c r="B460" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
+      <c r="D460" s="8">
+        <v>0</v>
+      </c>
+      <c r="E460" s="8"/>
+      <c r="F460" s="8"/>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A461" s="7">
+        <v>46009</v>
+      </c>
+      <c r="B461" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+      <c r="D461" s="8">
+        <v>0</v>
+      </c>
+      <c r="E461" s="8"/>
+      <c r="F461" s="8"/>
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A462" s="7">
+        <v>46009</v>
+      </c>
+      <c r="B462" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C462">
+        <v>1</v>
+      </c>
+      <c r="D462" s="8">
+        <v>1</v>
+      </c>
+      <c r="E462" s="8"/>
+      <c r="F462" s="8"/>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A463" s="7">
+        <v>46009</v>
+      </c>
+      <c r="B463" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C463">
+        <v>1</v>
+      </c>
+      <c r="D463" s="8">
+        <v>0</v>
+      </c>
+      <c r="E463" s="8"/>
+      <c r="F463" s="8"/>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A464" s="7">
+        <v>46009</v>
+      </c>
+      <c r="B464" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C464">
+        <v>1</v>
+      </c>
+      <c r="D464" s="8">
+        <v>1</v>
+      </c>
+      <c r="E464" s="8"/>
+      <c r="F464" s="8"/>
+    </row>
+    <row r="465" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A465" s="7">
+        <v>46008</v>
+      </c>
+      <c r="B465" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C465">
+        <v>1</v>
+      </c>
+      <c r="D465" s="8">
+        <v>0</v>
+      </c>
+      <c r="E465" s="8"/>
+      <c r="F465" s="8"/>
+    </row>
+    <row r="466" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A466" s="7">
+        <v>46008</v>
+      </c>
+      <c r="B466" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C466">
+        <v>1</v>
+      </c>
+      <c r="D466" s="8">
+        <v>0</v>
+      </c>
+      <c r="E466" s="8"/>
+      <c r="F466" s="8"/>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A467" s="7">
+        <v>46007</v>
+      </c>
+      <c r="B467" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C467">
+        <v>1</v>
+      </c>
+      <c r="D467" s="8">
+        <v>0</v>
+      </c>
+      <c r="E467" s="8"/>
+      <c r="F467" s="8"/>
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A468" s="7">
+        <v>46007</v>
+      </c>
+      <c r="B468" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C468">
+        <v>1</v>
+      </c>
+      <c r="D468" s="8">
+        <v>1</v>
+      </c>
+      <c r="E468" s="8"/>
+      <c r="F468" s="8"/>
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A469" s="7">
+        <v>46006</v>
+      </c>
+      <c r="B469" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C469">
+        <v>1</v>
+      </c>
+      <c r="D469" s="8">
+        <v>0</v>
+      </c>
+      <c r="E469" s="8"/>
+      <c r="F469" s="8"/>
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A470" s="7">
+        <v>46006</v>
+      </c>
+      <c r="B470" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C470">
+        <v>1</v>
+      </c>
+      <c r="D470" s="8">
+        <v>1</v>
+      </c>
+      <c r="E470" s="8"/>
+      <c r="F470" s="8"/>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A471" s="7">
+        <v>46006</v>
+      </c>
+      <c r="B471" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C471">
+        <v>1</v>
+      </c>
+      <c r="D471" s="8">
+        <v>1</v>
+      </c>
+      <c r="E471" s="8"/>
+      <c r="F471" s="8"/>
+    </row>
+    <row r="472" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A472" s="7">
+        <v>46003</v>
+      </c>
+      <c r="B472" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C472">
+        <v>1</v>
+      </c>
+      <c r="D472" s="8">
+        <v>1</v>
+      </c>
+      <c r="E472" s="8"/>
+      <c r="F472" s="8"/>
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A473" s="7">
+        <v>46003</v>
+      </c>
+      <c r="B473" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C473">
+        <v>1</v>
+      </c>
+      <c r="D473" s="8">
+        <v>1</v>
+      </c>
+      <c r="E473" s="8"/>
+      <c r="F473" s="8"/>
+    </row>
+    <row r="474" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A474" s="7">
+        <v>46002</v>
+      </c>
+      <c r="B474" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C474">
+        <v>1</v>
+      </c>
+      <c r="D474" s="8">
+        <v>1</v>
+      </c>
+      <c r="E474" s="8"/>
+      <c r="F474" s="8"/>
+    </row>
+    <row r="475" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A475" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B475" t="s">
+        <v>7</v>
+      </c>
+      <c r="C475">
+        <v>1</v>
+      </c>
+      <c r="D475">
+        <v>1</v>
+      </c>
+      <c r="E475" s="8"/>
+      <c r="F475" s="8"/>
+    </row>
+    <row r="476" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A476" s="4">
+        <v>46009</v>
+      </c>
+      <c r="E476">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A477" s="4">
+        <v>46002</v>
+      </c>
+      <c r="E477">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A478" s="4">
+        <v>46007</v>
+      </c>
+      <c r="E478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A479" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A480" s="5">
+        <v>46010</v>
+      </c>
+      <c r="E480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A481" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E481">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A482" s="4">
+        <v>46002</v>
+      </c>
+      <c r="E482">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A483" s="4">
+        <v>46002</v>
+      </c>
+      <c r="E483">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A484" s="4">
+        <v>46002</v>
+      </c>
+      <c r="E484">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A485" s="4">
+        <v>46003</v>
+      </c>
+      <c r="E485">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A486" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E486">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A487" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E487">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A488" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E488">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A489" s="4">
+        <v>46007</v>
+      </c>
+      <c r="E489">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A490" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E490">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A491" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E491">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A492" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E492">
         <v>1</v>
       </c>
     </row>
@@ -5784,6 +6176,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
+    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
+    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="USB-Dokument" ma:contentTypeID="0x01010074254FFFFA788748BE9570FD90FA56DE00A6BA077A5C2D0748B0D413E1B37C0DF4" ma:contentTypeVersion="19" ma:contentTypeDescription="Ein neues USB-Dokument in der Bibliothek erstellen." ma:contentTypeScope="" ma:versionID="d59990fbfd519ac7209fb148145d468e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee2de805-d424-449f-84ad-9da0e2dd7d39" xmlns:ns3="4c57b41f-cbf4-457f-bf80-bd53c8e26310" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9590e4e8f2b27359d78ddca2ab94a63e" ns2:_="" ns3:_="">
     <xsd:import namespace="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
@@ -6000,19 +6405,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
-    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
-    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
   <ds:schemaRefs>
@@ -6022,6 +6414,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46834C1C-4F65-47EA-B4E5-1EFA1FE1385B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6038,21 +6447,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1354" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF22474B-1145-8840-B1CA-F149940F1752}"/>
+  <xr:revisionPtr revIDLastSave="1484" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{221256BC-54D3-0D44-B3CF-130AFC646573}"/>
   <bookViews>
     <workbookView xWindow="5300" yWindow="820" windowWidth="40220" windowHeight="25920" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -489,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:G492"/>
+  <dimension ref="A1:G552"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -6062,7 +6062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A481" s="4">
         <v>46006</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A482" s="4">
         <v>46002</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A483" s="4">
         <v>46002</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A484" s="4">
         <v>46002</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A485" s="4">
         <v>46003</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
         <v>46010</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A487" s="4">
         <v>46010</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A488" s="4">
         <v>46006</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A489" s="4">
         <v>46007</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A490" s="4">
         <v>46010</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A491" s="4">
         <v>46006</v>
       </c>
@@ -6150,11 +6150,731 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A492" s="4">
         <v>46008</v>
       </c>
       <c r="E492">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A493" s="7">
+        <v>46050</v>
+      </c>
+      <c r="B493" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C493">
+        <v>1</v>
+      </c>
+      <c r="D493" s="8">
+        <v>0</v>
+      </c>
+      <c r="E493" s="9"/>
+      <c r="F493" s="8"/>
+    </row>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A494" s="7">
+        <v>46049</v>
+      </c>
+      <c r="B494" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C494">
+        <v>1</v>
+      </c>
+      <c r="D494" s="8">
+        <v>0</v>
+      </c>
+      <c r="E494" s="9"/>
+      <c r="F494" s="8"/>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A495" s="7">
+        <v>46049</v>
+      </c>
+      <c r="B495" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+      <c r="D495" s="8">
+        <v>1</v>
+      </c>
+      <c r="E495" s="9"/>
+      <c r="F495" s="8"/>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A496" s="7">
+        <v>46045</v>
+      </c>
+      <c r="B496" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C496">
+        <v>1</v>
+      </c>
+      <c r="D496" s="8">
+        <v>0</v>
+      </c>
+      <c r="E496" s="9"/>
+      <c r="F496" s="8"/>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A497" s="7">
+        <v>46045</v>
+      </c>
+      <c r="B497" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C497">
+        <v>1</v>
+      </c>
+      <c r="D497" s="8">
+        <v>0</v>
+      </c>
+      <c r="E497" s="9"/>
+      <c r="F497" s="8"/>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A498" s="7">
+        <v>46044</v>
+      </c>
+      <c r="B498" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C498">
+        <v>1</v>
+      </c>
+      <c r="D498" s="8">
+        <v>1</v>
+      </c>
+      <c r="E498" s="9"/>
+      <c r="F498" s="8"/>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A499" s="7">
+        <v>46043</v>
+      </c>
+      <c r="B499" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C499">
+        <v>1</v>
+      </c>
+      <c r="D499" s="8">
+        <v>1</v>
+      </c>
+      <c r="E499" s="9"/>
+      <c r="F499" s="8"/>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A500" s="7">
+        <v>46041</v>
+      </c>
+      <c r="B500" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C500">
+        <v>1</v>
+      </c>
+      <c r="D500" s="8">
+        <v>1</v>
+      </c>
+      <c r="E500" s="9"/>
+      <c r="F500" s="8"/>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A501" s="7">
+        <v>46037</v>
+      </c>
+      <c r="B501" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C501">
+        <v>1</v>
+      </c>
+      <c r="D501" s="8">
+        <v>1</v>
+      </c>
+      <c r="E501" s="9"/>
+      <c r="F501" s="8"/>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A502" s="7">
+        <v>46036</v>
+      </c>
+      <c r="B502" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C502">
+        <v>1</v>
+      </c>
+      <c r="D502" s="8">
+        <v>0</v>
+      </c>
+      <c r="E502" s="9"/>
+      <c r="F502" s="8"/>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A503" s="7">
+        <v>46036</v>
+      </c>
+      <c r="B503" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C503">
+        <v>1</v>
+      </c>
+      <c r="D503" s="8">
+        <v>1</v>
+      </c>
+      <c r="E503" s="9"/>
+      <c r="F503" s="8"/>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A504" s="7">
+        <v>46035</v>
+      </c>
+      <c r="B504" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C504">
+        <v>1</v>
+      </c>
+      <c r="D504" s="8">
+        <v>1</v>
+      </c>
+      <c r="E504" s="9"/>
+      <c r="F504" s="8"/>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A505" s="7">
+        <v>46035</v>
+      </c>
+      <c r="B505" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C505">
+        <v>1</v>
+      </c>
+      <c r="D505" s="8">
+        <v>0</v>
+      </c>
+      <c r="E505" s="9"/>
+      <c r="F505" s="8"/>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A506" s="7">
+        <v>46035</v>
+      </c>
+      <c r="B506" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C506">
+        <v>1</v>
+      </c>
+      <c r="D506" s="8">
+        <v>0</v>
+      </c>
+      <c r="E506" s="9"/>
+      <c r="F506" s="8"/>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A507" s="7">
+        <v>46034</v>
+      </c>
+      <c r="B507" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C507">
+        <v>1</v>
+      </c>
+      <c r="D507" s="8">
+        <v>0</v>
+      </c>
+      <c r="E507" s="9"/>
+      <c r="F507" s="8"/>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A508" s="7">
+        <v>46030</v>
+      </c>
+      <c r="B508" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C508">
+        <v>1</v>
+      </c>
+      <c r="D508" s="8">
+        <v>1</v>
+      </c>
+      <c r="E508" s="8"/>
+      <c r="F508" s="8"/>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A509" s="7">
+        <v>46029</v>
+      </c>
+      <c r="B509" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C509">
+        <v>1</v>
+      </c>
+      <c r="D509" s="8">
+        <v>0</v>
+      </c>
+      <c r="E509" s="8"/>
+      <c r="F509" s="8"/>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A510" s="7">
+        <v>46028</v>
+      </c>
+      <c r="B510" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C510">
+        <v>1</v>
+      </c>
+      <c r="D510" s="8">
+        <v>0</v>
+      </c>
+      <c r="E510" s="8"/>
+      <c r="F510" s="8"/>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A511" s="7">
+        <v>46028</v>
+      </c>
+      <c r="B511" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C511">
+        <v>1</v>
+      </c>
+      <c r="D511" s="8">
+        <v>0</v>
+      </c>
+      <c r="E511" s="8"/>
+      <c r="F511" s="8"/>
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A512" s="7">
+        <v>46027</v>
+      </c>
+      <c r="B512" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C512">
+        <v>1</v>
+      </c>
+      <c r="D512" s="8">
+        <v>1</v>
+      </c>
+      <c r="E512" s="8"/>
+      <c r="F512" s="8"/>
+    </row>
+    <row r="513" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A513" s="7">
+        <v>46027</v>
+      </c>
+      <c r="B513" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C513">
+        <v>1</v>
+      </c>
+      <c r="D513" s="8">
+        <v>1</v>
+      </c>
+      <c r="E513" s="8"/>
+      <c r="F513" s="8"/>
+    </row>
+    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A514" s="7">
+        <v>46027</v>
+      </c>
+      <c r="B514" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C514">
+        <v>1</v>
+      </c>
+      <c r="D514" s="8">
+        <v>1</v>
+      </c>
+      <c r="E514" s="8"/>
+      <c r="F514" s="8"/>
+    </row>
+    <row r="515" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A515" s="7">
+        <v>46022</v>
+      </c>
+      <c r="B515" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C515">
+        <v>1</v>
+      </c>
+      <c r="D515" s="8">
+        <v>0</v>
+      </c>
+      <c r="E515" s="8"/>
+      <c r="F515" s="8"/>
+    </row>
+    <row r="516" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A516" s="7">
+        <v>46022</v>
+      </c>
+      <c r="B516" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C516">
+        <v>1</v>
+      </c>
+      <c r="D516" s="8">
+        <v>0</v>
+      </c>
+      <c r="E516" s="8"/>
+      <c r="F516" s="8"/>
+    </row>
+    <row r="517" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A517" s="7">
+        <v>46022</v>
+      </c>
+      <c r="B517" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C517">
+        <v>1</v>
+      </c>
+      <c r="D517" s="8">
+        <v>0</v>
+      </c>
+      <c r="E517" s="8"/>
+      <c r="F517" s="8"/>
+    </row>
+    <row r="518" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A518" s="7">
+        <v>46020</v>
+      </c>
+      <c r="B518" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C518">
+        <v>1</v>
+      </c>
+      <c r="D518" s="8">
+        <v>0</v>
+      </c>
+      <c r="E518" s="8"/>
+      <c r="F518" s="8"/>
+    </row>
+    <row r="519" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A519" s="7">
+        <v>46014</v>
+      </c>
+      <c r="B519" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C519">
+        <v>1</v>
+      </c>
+      <c r="D519" s="8">
+        <v>0</v>
+      </c>
+      <c r="E519" s="9"/>
+      <c r="F519" s="8"/>
+    </row>
+    <row r="520" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A520" s="7">
+        <v>46014</v>
+      </c>
+      <c r="B520" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C520">
+        <v>1</v>
+      </c>
+      <c r="D520" s="8">
+        <v>1</v>
+      </c>
+      <c r="E520" s="9"/>
+      <c r="F520" s="8"/>
+    </row>
+    <row r="521" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A521" s="7">
+        <v>46010</v>
+      </c>
+      <c r="B521" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C521">
+        <v>1</v>
+      </c>
+      <c r="D521" s="8">
+        <v>0</v>
+      </c>
+      <c r="E521" s="9"/>
+      <c r="F521" s="8"/>
+    </row>
+    <row r="522" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A522" s="7">
+        <v>46010</v>
+      </c>
+      <c r="B522" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C522">
+        <v>1</v>
+      </c>
+      <c r="D522" s="8">
+        <v>0</v>
+      </c>
+      <c r="E522" s="9"/>
+      <c r="F522" s="8"/>
+    </row>
+    <row r="523" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A523" s="1">
+        <v>46045</v>
+      </c>
+      <c r="E523">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A524" s="1">
+        <v>46020</v>
+      </c>
+      <c r="E524">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A525" s="1">
+        <v>46010</v>
+      </c>
+      <c r="E525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A526" s="1">
+        <v>46050</v>
+      </c>
+      <c r="E526">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A527" s="1">
+        <v>46029</v>
+      </c>
+      <c r="E527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A528" s="1">
+        <v>46028</v>
+      </c>
+      <c r="E528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A529" s="1">
+        <v>46028</v>
+      </c>
+      <c r="E529">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A530" s="1">
+        <v>46021</v>
+      </c>
+      <c r="E530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A531" s="1">
+        <v>46050</v>
+      </c>
+      <c r="E531">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A532" s="1">
+        <v>46020</v>
+      </c>
+      <c r="E532">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A533" s="1">
+        <v>46048</v>
+      </c>
+      <c r="E533">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A534" s="1">
+        <v>46030</v>
+      </c>
+      <c r="E534">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A535" s="1">
+        <v>46042</v>
+      </c>
+      <c r="E535">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A536" s="1">
+        <v>46014</v>
+      </c>
+      <c r="E536">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A537" s="1">
+        <v>46043</v>
+      </c>
+      <c r="E537">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A538" s="1">
+        <v>46036</v>
+      </c>
+      <c r="E538">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A539" s="1">
+        <v>46013</v>
+      </c>
+      <c r="E539">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A540" s="1">
+        <v>46010</v>
+      </c>
+      <c r="E540">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A541" s="1">
+        <v>46014</v>
+      </c>
+      <c r="E541">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A542" s="1">
+        <v>46027</v>
+      </c>
+      <c r="E542">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A543" s="1">
+        <v>46028</v>
+      </c>
+      <c r="E543">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A544" s="1">
+        <v>46041</v>
+      </c>
+      <c r="E544">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A545" s="1">
+        <v>46044</v>
+      </c>
+      <c r="E545">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A546" s="1">
+        <v>46010</v>
+      </c>
+      <c r="E546">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A547" s="1">
+        <v>46042</v>
+      </c>
+      <c r="E547">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A548" s="1">
+        <v>46027</v>
+      </c>
+      <c r="E548">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A549" s="1">
+        <v>46049</v>
+      </c>
+      <c r="E549">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A550" s="1">
+        <v>46049</v>
+      </c>
+      <c r="E550">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A551" s="1">
+        <v>46045</v>
+      </c>
+      <c r="E551">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A552" s="1">
+        <v>46042</v>
+      </c>
+      <c r="E552">
         <v>1</v>
       </c>
     </row>
@@ -6167,15 +6887,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
@@ -6186,6 +6897,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6406,26 +7126,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1484" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{221256BC-54D3-0D44-B3CF-130AFC646573}"/>
+  <xr:revisionPtr revIDLastSave="1548" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA68B293-7A37-3F45-BABC-969AFCF0751A}"/>
   <bookViews>
     <workbookView xWindow="5300" yWindow="820" windowWidth="40220" windowHeight="25920" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -489,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:G552"/>
+  <dimension ref="A1:G580"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -6814,7 +6814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A545" s="1">
         <v>46044</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A546" s="1">
         <v>46010</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A547" s="1">
         <v>46042</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A548" s="1">
         <v>46027</v>
       </c>
@@ -6846,7 +6846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A549" s="1">
         <v>46049</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A550" s="1">
         <v>46049</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A551" s="1">
         <v>46045</v>
       </c>
@@ -6870,11 +6870,347 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A552" s="1">
         <v>46042</v>
       </c>
       <c r="E552">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A553" s="7">
+        <v>46079</v>
+      </c>
+      <c r="B553" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C553">
+        <v>1</v>
+      </c>
+      <c r="D553" s="8">
+        <v>0</v>
+      </c>
+      <c r="E553" s="8"/>
+      <c r="F553" s="8"/>
+    </row>
+    <row r="554" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A554" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B554" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C554">
+        <v>1</v>
+      </c>
+      <c r="D554" s="8">
+        <v>0</v>
+      </c>
+      <c r="E554" s="8"/>
+      <c r="F554" s="8"/>
+    </row>
+    <row r="555" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A555" s="7">
+        <v>46078</v>
+      </c>
+      <c r="B555" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C555">
+        <v>1</v>
+      </c>
+      <c r="D555" s="8">
+        <v>1</v>
+      </c>
+      <c r="E555" s="8"/>
+      <c r="F555" s="8"/>
+    </row>
+    <row r="556" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A556" s="7">
+        <v>46073</v>
+      </c>
+      <c r="B556" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C556">
+        <v>1</v>
+      </c>
+      <c r="D556" s="8">
+        <v>1</v>
+      </c>
+      <c r="E556" s="8"/>
+      <c r="F556" s="8"/>
+    </row>
+    <row r="557" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A557" s="7">
+        <v>46072</v>
+      </c>
+      <c r="B557" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C557">
+        <v>1</v>
+      </c>
+      <c r="D557" s="8">
+        <v>0</v>
+      </c>
+      <c r="E557" s="8"/>
+      <c r="F557" s="8"/>
+    </row>
+    <row r="558" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A558" s="7">
+        <v>46071</v>
+      </c>
+      <c r="B558" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C558">
+        <v>1</v>
+      </c>
+      <c r="D558" s="8">
+        <v>0</v>
+      </c>
+      <c r="E558" s="8"/>
+      <c r="F558" s="8"/>
+    </row>
+    <row r="559" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A559" s="7">
+        <v>46069</v>
+      </c>
+      <c r="B559" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C559">
+        <v>1</v>
+      </c>
+      <c r="D559" s="8">
+        <v>1</v>
+      </c>
+      <c r="E559" s="8"/>
+      <c r="F559" s="8"/>
+    </row>
+    <row r="560" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A560" s="7">
+        <v>46069</v>
+      </c>
+      <c r="B560" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C560">
+        <v>1</v>
+      </c>
+      <c r="D560" s="8">
+        <v>1</v>
+      </c>
+      <c r="E560" s="8"/>
+      <c r="F560" s="8"/>
+    </row>
+    <row r="561" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A561" s="7">
+        <v>46064</v>
+      </c>
+      <c r="B561" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C561">
+        <v>1</v>
+      </c>
+      <c r="D561" s="8">
+        <v>0</v>
+      </c>
+      <c r="E561" s="8"/>
+      <c r="F561" s="8"/>
+    </row>
+    <row r="562" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A562" s="7">
+        <v>46063</v>
+      </c>
+      <c r="B562" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C562">
+        <v>1</v>
+      </c>
+      <c r="D562" s="8">
+        <v>1</v>
+      </c>
+      <c r="E562" s="8"/>
+      <c r="F562" s="8"/>
+    </row>
+    <row r="563" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A563" s="7">
+        <v>46063</v>
+      </c>
+      <c r="B563" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C563">
+        <v>1</v>
+      </c>
+      <c r="D563" s="8">
+        <v>0</v>
+      </c>
+      <c r="E563" s="8"/>
+      <c r="F563" s="8"/>
+    </row>
+    <row r="564" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A564" s="7">
+        <v>46062</v>
+      </c>
+      <c r="B564" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C564">
+        <v>1</v>
+      </c>
+      <c r="D564" s="8">
+        <v>0</v>
+      </c>
+      <c r="E564" s="8"/>
+      <c r="F564" s="8"/>
+    </row>
+    <row r="565" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A565" s="7">
+        <v>46059</v>
+      </c>
+      <c r="B565" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C565">
+        <v>1</v>
+      </c>
+      <c r="D565" s="8">
+        <v>1</v>
+      </c>
+      <c r="E565" s="8"/>
+      <c r="F565" s="8"/>
+    </row>
+    <row r="566" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A566" s="7">
+        <v>46055</v>
+      </c>
+      <c r="B566" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C566">
+        <v>1</v>
+      </c>
+      <c r="D566" s="8">
+        <v>1</v>
+      </c>
+      <c r="E566" s="8"/>
+      <c r="F566" s="8"/>
+    </row>
+    <row r="567" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A567" s="1">
+        <v>46079</v>
+      </c>
+      <c r="E567">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A568" s="1">
+        <v>46056</v>
+      </c>
+      <c r="E568">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A569" s="1">
+        <v>46051</v>
+      </c>
+      <c r="E569">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A570" s="1">
+        <v>46063</v>
+      </c>
+      <c r="E570">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A571" s="1">
+        <v>46062</v>
+      </c>
+      <c r="E571">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A572" s="1">
+        <v>46062</v>
+      </c>
+      <c r="E572">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A573" s="1">
+        <v>46057</v>
+      </c>
+      <c r="E573">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A574" s="1">
+        <v>46056</v>
+      </c>
+      <c r="E574">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A575" s="1">
+        <v>46076</v>
+      </c>
+      <c r="E575">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A576" s="1">
+        <v>46055</v>
+      </c>
+      <c r="E576">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A577" s="1">
+        <v>46077</v>
+      </c>
+      <c r="E577">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A578" s="1">
+        <v>46070</v>
+      </c>
+      <c r="E578">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A579" s="1">
+        <v>46052</v>
+      </c>
+      <c r="E579">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A580" s="1">
+        <v>46051</v>
+      </c>
+      <c r="E580">
         <v>1</v>
       </c>
     </row>
@@ -6887,6 +7223,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
@@ -6899,18 +7244,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="USB-Dokument" ma:contentTypeID="0x01010074254FFFFA788748BE9570FD90FA56DE00A6BA077A5C2D0748B0D413E1B37C0DF4" ma:contentTypeVersion="19" ma:contentTypeDescription="Ein neues USB-Dokument in der Bibliothek erstellen." ma:contentTypeScope="" ma:versionID="d59990fbfd519ac7209fb148145d468e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee2de805-d424-449f-84ad-9da0e2dd7d39" xmlns:ns3="4c57b41f-cbf4-457f-bf80-bd53c8e26310" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9590e4e8f2b27359d78ddca2ab94a63e" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="USB-Dokument" ma:contentTypeID="0x01010074254FFFFA788748BE9570FD90FA56DE00A6BA077A5C2D0748B0D413E1B37C0DF4" ma:contentTypeVersion="19" ma:contentTypeDescription="Ein neues USB-Dokument in der Bibliothek erstellen." ma:contentTypeScope="" ma:versionID="c510736d7b8df5493d0c0cbf1b659039">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee2de805-d424-449f-84ad-9da0e2dd7d39" xmlns:ns3="4c57b41f-cbf4-457f-bf80-bd53c8e26310" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="30d006a702a85f058c7f942dd83db01e" ns2:_="" ns3:_="">
     <xsd:import namespace="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
     <xsd:import namespace="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
     <xsd:element name="properties">
@@ -7126,23 +7462,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -7150,8 +7469,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46834C1C-4F65-47EA-B4E5-1EFA1FE1385B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E67CF1-8A7B-44D0-A2A1-F624F69C8C2A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>

--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1548" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA68B293-7A37-3F45-BABC-969AFCF0751A}"/>
+  <xr:revisionPtr revIDLastSave="1580" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E214C68-3558-B14F-9498-5710B2988386}"/>
   <bookViews>
-    <workbookView xWindow="5300" yWindow="820" windowWidth="40220" windowHeight="25920" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="17100" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -155,6 +155,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -489,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:G580"/>
+  <dimension ref="A1:G616"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -7103,7 +7104,7 @@
       <c r="F566" s="8"/>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A567" s="1">
+      <c r="A567" s="4">
         <v>46079</v>
       </c>
       <c r="E567">
@@ -7111,7 +7112,7 @@
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A568" s="1">
+      <c r="A568" s="4">
         <v>46056</v>
       </c>
       <c r="E568">
@@ -7119,7 +7120,7 @@
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A569" s="1">
+      <c r="A569" s="4">
         <v>46051</v>
       </c>
       <c r="E569">
@@ -7127,7 +7128,7 @@
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A570" s="1">
+      <c r="A570" s="4">
         <v>46063</v>
       </c>
       <c r="E570">
@@ -7135,7 +7136,7 @@
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A571" s="1">
+      <c r="A571" s="4">
         <v>46062</v>
       </c>
       <c r="E571">
@@ -7143,7 +7144,7 @@
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A572" s="1">
+      <c r="A572" s="4">
         <v>46062</v>
       </c>
       <c r="E572">
@@ -7151,7 +7152,7 @@
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A573" s="1">
+      <c r="A573" s="4">
         <v>46057</v>
       </c>
       <c r="E573">
@@ -7159,7 +7160,7 @@
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A574" s="1">
+      <c r="A574" s="4">
         <v>46056</v>
       </c>
       <c r="E574">
@@ -7167,7 +7168,7 @@
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A575" s="1">
+      <c r="A575" s="4">
         <v>46076</v>
       </c>
       <c r="E575">
@@ -7175,42 +7176,510 @@
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A576" s="1">
+      <c r="A576" s="4">
         <v>46055</v>
       </c>
       <c r="E576">
         <v>1</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A577" s="1">
+    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A577" s="4">
         <v>46077</v>
       </c>
       <c r="E577">
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A578" s="1">
+    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A578" s="4">
         <v>46070</v>
       </c>
       <c r="E578">
         <v>1</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A579" s="1">
+    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A579" s="4">
         <v>46052</v>
       </c>
       <c r="E579">
         <v>1</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A580" s="1">
+    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A580" s="4">
         <v>46051</v>
       </c>
       <c r="E580">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A581" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B581" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C581" s="8">
+        <v>1</v>
+      </c>
+      <c r="D581" s="8">
+        <v>0</v>
+      </c>
+      <c r="E581" s="8"/>
+      <c r="F581" s="8"/>
+      <c r="G581" s="8"/>
+    </row>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A582" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B582" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C582" s="8">
+        <v>1</v>
+      </c>
+      <c r="D582" s="8">
+        <v>0</v>
+      </c>
+      <c r="E582" s="8"/>
+      <c r="F582" s="8"/>
+      <c r="G582" s="8"/>
+    </row>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A583" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B583" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C583" s="8">
+        <v>1</v>
+      </c>
+      <c r="D583" s="8">
+        <v>1</v>
+      </c>
+      <c r="E583" s="8"/>
+      <c r="F583" s="8"/>
+      <c r="G583" s="8"/>
+    </row>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A584" s="7">
+        <v>46104</v>
+      </c>
+      <c r="B584" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C584" s="8">
+        <v>1</v>
+      </c>
+      <c r="D584" s="8">
+        <v>1</v>
+      </c>
+      <c r="E584" s="8"/>
+      <c r="F584" s="8"/>
+      <c r="G584" s="8"/>
+    </row>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A585" s="7">
+        <v>46101</v>
+      </c>
+      <c r="B585" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C585" s="8">
+        <v>1</v>
+      </c>
+      <c r="D585" s="8">
+        <v>0</v>
+      </c>
+      <c r="E585" s="8"/>
+      <c r="F585" s="8"/>
+      <c r="G585" s="8"/>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A586" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B586" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C586" s="8">
+        <v>1</v>
+      </c>
+      <c r="D586" s="8">
+        <v>1</v>
+      </c>
+      <c r="E586" s="8"/>
+      <c r="F586" s="8"/>
+      <c r="G586" s="8"/>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A587" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B587" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C587" s="8">
+        <v>1</v>
+      </c>
+      <c r="D587" s="8">
+        <v>0</v>
+      </c>
+      <c r="E587" s="8"/>
+      <c r="F587" s="8"/>
+      <c r="G587" s="8"/>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A588" s="7">
+        <v>46098</v>
+      </c>
+      <c r="B588" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C588" s="8">
+        <v>1</v>
+      </c>
+      <c r="D588" s="8">
+        <v>1</v>
+      </c>
+      <c r="E588" s="8"/>
+      <c r="F588" s="8"/>
+      <c r="G588" s="8"/>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A589" s="7">
+        <v>46098</v>
+      </c>
+      <c r="B589" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C589" s="8">
+        <v>1</v>
+      </c>
+      <c r="D589" s="8">
+        <v>1</v>
+      </c>
+      <c r="E589" s="8"/>
+      <c r="F589" s="8"/>
+      <c r="G589" s="8"/>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A590" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B590" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C590" s="8">
+        <v>1</v>
+      </c>
+      <c r="D590" s="8">
+        <v>0</v>
+      </c>
+      <c r="E590" s="8"/>
+      <c r="F590" s="8"/>
+      <c r="G590" s="8"/>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A591" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B591" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C591" s="8">
+        <v>1</v>
+      </c>
+      <c r="D591" s="8">
+        <v>0</v>
+      </c>
+      <c r="E591" s="8"/>
+      <c r="F591" s="8"/>
+      <c r="G591" s="8"/>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A592" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B592" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C592" s="8">
+        <v>1</v>
+      </c>
+      <c r="D592" s="8">
+        <v>0</v>
+      </c>
+      <c r="E592" s="8"/>
+      <c r="F592" s="8"/>
+      <c r="G592" s="8"/>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A593" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B593" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C593" s="8">
+        <v>1</v>
+      </c>
+      <c r="D593" s="8">
+        <v>1</v>
+      </c>
+      <c r="E593" s="8"/>
+      <c r="F593" s="8"/>
+      <c r="G593" s="8"/>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A594" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B594" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C594" s="8">
+        <v>1</v>
+      </c>
+      <c r="D594" s="8">
+        <v>1</v>
+      </c>
+      <c r="E594" s="8"/>
+      <c r="F594" s="8"/>
+      <c r="G594" s="8"/>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A595" s="7">
+        <v>46086</v>
+      </c>
+      <c r="B595" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C595" s="8">
+        <v>1</v>
+      </c>
+      <c r="D595" s="8">
+        <v>0</v>
+      </c>
+      <c r="E595" s="8"/>
+      <c r="F595" s="8"/>
+      <c r="G595" s="8"/>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A596" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B596" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C596" s="8">
+        <v>1</v>
+      </c>
+      <c r="D596" s="8">
+        <v>1</v>
+      </c>
+      <c r="E596" s="8"/>
+      <c r="F596" s="8"/>
+      <c r="G596" s="8"/>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A597" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B597" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C597" s="8">
+        <v>1</v>
+      </c>
+      <c r="D597" s="8">
+        <v>1</v>
+      </c>
+      <c r="E597" s="8"/>
+      <c r="F597" s="8"/>
+      <c r="G597" s="8"/>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A598" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B598" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C598" s="8">
+        <v>1</v>
+      </c>
+      <c r="D598" s="8">
+        <v>1</v>
+      </c>
+      <c r="E598" s="8"/>
+      <c r="F598" s="8"/>
+      <c r="G598" s="8"/>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A599" s="10">
+        <v>46079</v>
+      </c>
+      <c r="B599" s="10"/>
+      <c r="E599">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A600" s="10">
+        <v>46083</v>
+      </c>
+      <c r="B600" s="10"/>
+      <c r="E600">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A601" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B601" s="10"/>
+      <c r="E601">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A602" s="10">
+        <v>46086</v>
+      </c>
+      <c r="B602" s="10"/>
+      <c r="E602">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A603" s="10">
+        <v>46090</v>
+      </c>
+      <c r="B603" s="10"/>
+      <c r="E603">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A604" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B604" s="10"/>
+      <c r="E604">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A605" s="10">
+        <v>46092</v>
+      </c>
+      <c r="B605" s="10"/>
+      <c r="E605">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A606" s="10">
+        <v>46093</v>
+      </c>
+      <c r="B606" s="10"/>
+      <c r="E606">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A607" s="10">
+        <v>46094</v>
+      </c>
+      <c r="B607" s="10"/>
+      <c r="E607">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A608" s="10">
+        <v>46097</v>
+      </c>
+      <c r="B608" s="10"/>
+      <c r="E608">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A609" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B609" s="10"/>
+      <c r="E609">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A610" s="10">
+        <v>46099</v>
+      </c>
+      <c r="B610" s="10"/>
+      <c r="E610">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A611" s="10">
+        <v>46100</v>
+      </c>
+      <c r="B611" s="10"/>
+      <c r="E611">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A612" s="10">
+        <v>46101</v>
+      </c>
+      <c r="B612" s="10"/>
+      <c r="E612">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A613" s="10">
+        <v>46104</v>
+      </c>
+      <c r="B613" s="10"/>
+      <c r="E613">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A614" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B614" s="10"/>
+      <c r="E614">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A615" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B615" s="10"/>
+      <c r="E615">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A616" s="10">
+        <v>46107</v>
+      </c>
+      <c r="B616" s="10"/>
+      <c r="E616">
         <v>1</v>
       </c>
     </row>
@@ -7223,28 +7692,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
-    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
-    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="USB-Dokument" ma:contentTypeID="0x01010074254FFFFA788748BE9570FD90FA56DE00A6BA077A5C2D0748B0D413E1B37C0DF4" ma:contentTypeVersion="19" ma:contentTypeDescription="Ein neues USB-Dokument in der Bibliothek erstellen." ma:contentTypeScope="" ma:versionID="c510736d7b8df5493d0c0cbf1b659039">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee2de805-d424-449f-84ad-9da0e2dd7d39" xmlns:ns3="4c57b41f-cbf4-457f-bf80-bd53c8e26310" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="30d006a702a85f058c7f942dd83db01e" ns2:_="" ns3:_="">
     <xsd:import namespace="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
@@ -7461,32 +7908,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
+    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
+    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E67CF1-8A7B-44D0-A2A1-F624F69C8C2A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7503,4 +7947,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1580" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E214C68-3558-B14F-9498-5710B2988386}"/>
+  <xr:revisionPtr revIDLastSave="1622" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8506601-19C5-E548-9AE6-CE95BF655343}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="17100" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
+    <workbookView xWindow="23360" yWindow="3480" windowWidth="25820" windowHeight="17100" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -490,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:G616"/>
+  <dimension ref="A1:G650"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -7611,7 +7611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A609" s="10">
         <v>46098</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A610" s="10">
         <v>46099</v>
       </c>
@@ -7629,7 +7629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A611" s="10">
         <v>46100</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A612" s="10">
         <v>46101</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A613" s="10">
         <v>46104</v>
       </c>
@@ -7656,7 +7656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A614" s="10">
         <v>46105</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A615" s="10">
         <v>46105</v>
       </c>
@@ -7674,12 +7674,403 @@
         <v>1</v>
       </c>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A616" s="10">
         <v>46107</v>
       </c>
       <c r="B616" s="10"/>
       <c r="E616">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A617" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B617" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C617" s="8">
+        <v>1</v>
+      </c>
+      <c r="D617" s="8">
+        <v>0</v>
+      </c>
+      <c r="F617" s="8"/>
+    </row>
+    <row r="618" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A618" s="7">
+        <v>45799</v>
+      </c>
+      <c r="B618" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C618" s="8">
+        <v>1</v>
+      </c>
+      <c r="D618" s="8">
+        <v>0</v>
+      </c>
+      <c r="F618" s="8"/>
+    </row>
+    <row r="619" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A619" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B619" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C619" s="8">
+        <v>1</v>
+      </c>
+      <c r="D619" s="8">
+        <v>0</v>
+      </c>
+      <c r="F619" s="8"/>
+    </row>
+    <row r="620" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A620" s="7">
+        <v>46140</v>
+      </c>
+      <c r="B620" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C620" s="8">
+        <v>1</v>
+      </c>
+      <c r="D620" s="8">
+        <v>0</v>
+      </c>
+      <c r="F620" s="8"/>
+    </row>
+    <row r="621" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A621" s="7">
+        <v>46139</v>
+      </c>
+      <c r="B621" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C621" s="8">
+        <v>1</v>
+      </c>
+      <c r="D621" s="8">
+        <v>0</v>
+      </c>
+      <c r="F621" s="8"/>
+    </row>
+    <row r="622" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A622" s="7">
+        <v>46139</v>
+      </c>
+      <c r="B622" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C622" s="8">
+        <v>1</v>
+      </c>
+      <c r="D622" s="8">
+        <v>0</v>
+      </c>
+      <c r="F622" s="8"/>
+    </row>
+    <row r="623" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A623" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B623" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C623" s="8">
+        <v>1</v>
+      </c>
+      <c r="D623" s="8">
+        <v>0</v>
+      </c>
+      <c r="F623" s="8"/>
+    </row>
+    <row r="624" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A624" s="7">
+        <v>46134</v>
+      </c>
+      <c r="B624" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C624" s="8">
+        <v>1</v>
+      </c>
+      <c r="D624" s="8">
+        <v>1</v>
+      </c>
+      <c r="F624" s="8"/>
+    </row>
+    <row r="625" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A625" s="7">
+        <v>46132</v>
+      </c>
+      <c r="B625" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C625" s="8">
+        <v>1</v>
+      </c>
+      <c r="D625" s="8">
+        <v>0</v>
+      </c>
+      <c r="F625" s="8"/>
+    </row>
+    <row r="626" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A626" s="7">
+        <v>46126</v>
+      </c>
+      <c r="B626" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C626" s="8">
+        <v>1</v>
+      </c>
+      <c r="D626" s="8">
+        <v>0</v>
+      </c>
+      <c r="F626" s="8"/>
+    </row>
+    <row r="627" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A627" s="7">
+        <v>46126</v>
+      </c>
+      <c r="B627" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C627" s="8">
+        <v>1</v>
+      </c>
+      <c r="D627" s="8">
+        <v>0</v>
+      </c>
+      <c r="F627" s="8"/>
+    </row>
+    <row r="628" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A628" s="7">
+        <v>46125</v>
+      </c>
+      <c r="B628" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C628" s="8">
+        <v>1</v>
+      </c>
+      <c r="D628" s="8">
+        <v>1</v>
+      </c>
+      <c r="F628" s="8"/>
+    </row>
+    <row r="629" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A629" s="7">
+        <v>46121</v>
+      </c>
+      <c r="B629" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C629" s="8">
+        <v>1</v>
+      </c>
+      <c r="D629" s="8">
+        <v>0</v>
+      </c>
+      <c r="F629" s="8"/>
+    </row>
+    <row r="630" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A630" s="7">
+        <v>46062</v>
+      </c>
+      <c r="B630" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C630" s="8">
+        <v>1</v>
+      </c>
+      <c r="D630" s="8">
+        <v>0</v>
+      </c>
+      <c r="F630" s="8"/>
+    </row>
+    <row r="631" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A631" s="7">
+        <v>46120</v>
+      </c>
+      <c r="B631" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C631" s="8">
+        <v>1</v>
+      </c>
+      <c r="D631" s="8">
+        <v>0</v>
+      </c>
+      <c r="F631" s="8"/>
+    </row>
+    <row r="632" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A632" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B632" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C632" s="8">
+        <v>1</v>
+      </c>
+      <c r="D632" s="8">
+        <v>1</v>
+      </c>
+      <c r="F632" s="8"/>
+    </row>
+    <row r="633" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A633" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B633" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C633" s="8">
+        <v>1</v>
+      </c>
+      <c r="D633" s="8">
+        <v>1</v>
+      </c>
+      <c r="F633" s="8"/>
+    </row>
+    <row r="634" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A634" s="10">
+        <v>46108</v>
+      </c>
+      <c r="E634">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A635" s="10">
+        <v>46111</v>
+      </c>
+      <c r="E635">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A636" s="10">
+        <v>46114</v>
+      </c>
+      <c r="E636">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A637" s="10">
+        <v>46119</v>
+      </c>
+      <c r="E637">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A638" s="10">
+        <v>46119</v>
+      </c>
+      <c r="E638">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A639" s="10">
+        <v>46121</v>
+      </c>
+      <c r="E639">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A640" s="10">
+        <v>46122</v>
+      </c>
+      <c r="E640">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A641" s="10">
+        <v>46125</v>
+      </c>
+      <c r="E641">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A642" s="10">
+        <v>46126</v>
+      </c>
+      <c r="E642">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A643" s="10">
+        <v>46128</v>
+      </c>
+      <c r="E643">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A644" s="10">
+        <v>46129</v>
+      </c>
+      <c r="E644">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A645" s="10">
+        <v>46132</v>
+      </c>
+      <c r="E645">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A646" s="10">
+        <v>46133</v>
+      </c>
+      <c r="E646">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A647" s="10">
+        <v>46135</v>
+      </c>
+      <c r="E647">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A648" s="10">
+        <v>46136</v>
+      </c>
+      <c r="E648">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A649" s="10">
+        <v>46140</v>
+      </c>
+      <c r="E649">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A650" s="10">
+        <v>46141</v>
+      </c>
+      <c r="E650">
         <v>1</v>
       </c>
     </row>
@@ -7692,6 +8083,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
+    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
+    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="USB-Dokument" ma:contentTypeID="0x01010074254FFFFA788748BE9570FD90FA56DE00A6BA077A5C2D0748B0D413E1B37C0DF4" ma:contentTypeVersion="19" ma:contentTypeDescription="Ein neues USB-Dokument in der Bibliothek erstellen." ma:contentTypeScope="" ma:versionID="c510736d7b8df5493d0c0cbf1b659039">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee2de805-d424-449f-84ad-9da0e2dd7d39" xmlns:ns3="4c57b41f-cbf4-457f-bf80-bd53c8e26310" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="30d006a702a85f058c7f942dd83db01e" ns2:_="" ns3:_="">
     <xsd:import namespace="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
@@ -7908,29 +8321,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
-    <Patientdata xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">false</Patientdata>
-    <TaxCatchAll xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c57b41f-cbf4-457f-bf80-bd53c8e26310">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E67CF1-8A7B-44D0-A2A1-F624F69C8C2A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7947,29 +8363,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>